--- a/business_report_forms/031_emergency_distribution_swot_analysis--business_report_forms.xlsx
+++ b/business_report_forms/031_emergency_distribution_swot_analysis--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strong_leadership',_'value':_'strong_leadership'}</t>
+          <t>strong_leadership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strong Leadership', 'value': 'Strong Leadership'}</t>
+          <t>Strong Leadership</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'effective_communication',_'value':_'effective_communication'}</t>
+          <t>effective_communication</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Effective Communication', 'value': 'Effective Communication'}</t>
+          <t>Effective Communication</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'clear_goals',_'value':_'clear_goals'}</t>
+          <t>clear_goals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Clear Goals', 'value': 'Clear Goals'}</t>
+          <t>Clear Goals</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'strong_team',_'value':_'strong_team'}</t>
+          <t>strong_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Strong Team', 'value': 'Strong Team'}</t>
+          <t>Strong Team</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'poor_planning',_'value':_'poor_planning'}</t>
+          <t>poor_planning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Poor Planning', 'value': 'Poor Planning'}</t>
+          <t>Poor Planning</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'limited_resources',_'value':_'limited_resources'}</t>
+          <t>limited_resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Limited Resources', 'value': 'Limited Resources'}</t>
+          <t>Limited Resources</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'insufficient_training',_'value':_'insufficient_training'}</t>
+          <t>insufficient_training</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Insufficient Training', 'value': 'Insufficient Training'}</t>
+          <t>Insufficient Training</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'lack_of_coordination',_'value':_'lack_of_coordination'}</t>
+          <t>lack_of_coordination</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Lack of Coordination', 'value': 'Lack of Coordination'}</t>
+          <t>Lack of Coordination</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'natural_disasters',_'value':_'natural_disasters'}</t>
+          <t>natural_disasters</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Natural Disasters', 'value': 'Natural Disasters'}</t>
+          <t>Natural Disasters</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'economic_downturn',_'value':_'economic_downturn'}</t>
+          <t>economic_downturn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Economic Downturn', 'value': 'Economic Downturn'}</t>
+          <t>Economic Downturn</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'government_restrictions',_'value':_'government_restrictions'}</t>
+          <t>government_restrictions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Government Restrictions', 'value': 'Government Restrictions'}</t>
+          <t>Government Restrictions</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'global_conflict',_'value':_'global_conflict'}</t>
+          <t>global_conflict</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Global Conflict', 'value': 'Global Conflict'}</t>
+          <t>Global Conflict</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new_markets',_'value':_'new_markets'}</t>
+          <t>new_markets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New Markets', 'value': 'New Markets'}</t>
+          <t>New Markets</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'new_technology',_'value':_'new_technology'}</t>
+          <t>new_technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'New Technology', 'value': 'New Technology'}</t>
+          <t>New Technology</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'increased_funding',_'value':_'increased_funding'}</t>
+          <t>increased_funding</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Increased Funding', 'value': 'Increased Funding'}</t>
+          <t>Increased Funding</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'improved_processes',_'value':_'improved_processes'}</t>
+          <t>improved_processes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Improved Processes', 'value': 'Improved Processes'}</t>
+          <t>Improved Processes</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'non-governmental_organization',_'value':_'non-governmental_organization'}</t>
+          <t>non-governmental_organization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Non-Governmental Organization', 'value': 'Non-Governmental Organization'}</t>
+          <t>Non-Governmental Organization</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'government_organization',_'value':_'government_organization'}</t>
+          <t>government_organization</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Government Organization', 'value': 'Government Organization'}</t>
+          <t>Government Organization</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'private_sector',_'value':_'private_sector'}</t>
+          <t>private_sector</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Private Sector', 'value': 'Private Sector'}</t>
+          <t>Private Sector</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'logistics_and_supply_chain',_'value':_'logistics_and_supply_chain'}</t>
+          <t>logistics_and_supply_chain</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Logistics and Supply Chain', 'value': 'Logistics and Supply Chain'}</t>
+          <t>Logistics and Supply Chain</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medical_response',_'value':_'medical_response'}</t>
+          <t>medical_response</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medical Response', 'value': 'Medical Response'}</t>
+          <t>Medical Response</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'food_and_water_distribution',_'value':_'food_and_water_distribution'}</t>
+          <t>food_and_water_distribution</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Food and Water Distribution', 'value': 'Food and Water Distribution'}</t>
+          <t>Food and Water Distribution</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'emergency_shelter',_'value':_'emergency_shelter'}</t>
+          <t>emergency_shelter</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Emergency Shelter', 'value': 'Emergency Shelter'}</t>
+          <t>Emergency Shelter</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'food_and_water_distribution',_'value':_'food_and_water_distribution'}</t>
+          <t>food_and_water_distribution</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Food and Water Distribution', 'value': 'Food and Water Distribution'}</t>
+          <t>Food and Water Distribution</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'logistics_and_supply_chain',_'value':_'logistics_and_supply_chain'}</t>
+          <t>logistics_and_supply_chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Logistics and Supply Chain', 'value': 'Logistics and Supply Chain'}</t>
+          <t>Logistics and Supply Chain</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volunteer',_'value':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volunteer', 'value': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
